--- a/output/第10期計画_概要版の構成案.xlsx
+++ b/output/第10期計画_概要版の構成案.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_本編との対応" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_パブリックコメントと2版構成" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_決定を要する事項" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_レッドチームレビュー" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_自己点検記録" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -729,7 +729,7 @@
     <row r="15" ht="39" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>注1）本表は受託者の案であり、頁数・体裁・掲載内容の決定は発注者による（必要事項の一覧 成果品の仕様No.4）。注2）概要版は電子データのみの納品であり、印刷200部の対象は計画書本体である（仕様書４(10)）。したがって色数の制約は計画書本体（本文1色）とは異なり、概要版は多色で作成できる。ただし住民が自宅で白黒印刷することを想定し、白黒でも判読できる図表とする。注3）本表の頁割は、本編（素案 第11稿）の構成に対応している。本編の構成が変われば頁割も変わる。</t>
+          <t>注1）本表は受託者の案であり、頁数・体裁・掲載内容の決定は発注者による（必要事項の一覧 成果品の仕様No.4）。注2）概要版は電子データのみの納品であり、印刷200部の対象は計画書本体である（仕様書４(10)）。したがって色数の制約は計画書本体（本文1色）とは異なり、概要版は多色で作成できる。ただし住民が自宅で白黒印刷することを想定し、白黒でも判読できる図表とする。注3）本表の頁割は、本編（計画素案）の構成に対応している。本編の構成が変われば頁割も変わる。</t>
         </is>
       </c>
     </row>
@@ -859,7 +859,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>★意見を求めたい箇所を明示する。本編の該当頁を示す。意見提出の方法・期限・提出先を裏表紙に置く</t>
+          <t>意見を求めたい箇所を明示する。本編の該当頁を示す。意見提出の方法・期限・提出先を裏表紙に置く</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>★町別の比較を載せる。3町を一律に扱わない計画であることを示す</t>
+          <t>町別の比較を載せる。3町を一律に扱わない計画であることを示す</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>★試算値であることを明示して幅で示す（00シート④）。確定後に最終版で差し替える</t>
+          <t>試算値であることを明示して幅で示す（00シート④）。確定後に最終版で差し替える</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>★存在する場合はご提供をお願いする。体裁を踏襲することで住民の混乱を避けられる。07シートの決定事項No.2に含めた</t>
+          <t>存在する場合はご提供をお願いする。体裁を踏襲することで住民の混乱を避けられる。07シートの決定事項No.2に含めた</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>★B案。章と頁が1対1で対応するため、本編に戻りやすい</t>
+          <t>B案。章と頁が1対1で対応するため、本編に戻りやすい</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>★B案。1頁2点で、図表と本文の均衡が取れる</t>
+          <t>B案。1頁2点で、図表と本文の均衡が取れる</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>★B案以上。第9期の評価は仕様書４（1）(2)の中心であり、省略できない</t>
+          <t>B案以上。第9期の評価は仕様書４（1）(2)の中心であり、省略できない</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>★B案。所得段階別の表は本編に譲る</t>
+          <t>B案。所得段階別の表は本編に譲る</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>★B案。町別の頁を独立させると町の優劣の比較と受け取られやすい</t>
+          <t>B案。町別の頁を独立させると町の優劣の比較と受け取られやすい</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>★B案。8頁は自治体の広報折込と同程度の分量</t>
+          <t>B案。8頁は自治体の広報折込と同程度の分量</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>★A案・B案。C案は印刷の負担が大きい</t>
+          <t>A案・B案。C案は印刷の負担が大きい</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>★B案。論点は6件程度が住民の判断できる上限</t>
+          <t>B案。論点は6件程度が住民の判断できる上限</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>人口と高齢化の推移／要介護認定者数と認定率／高齢者のいる世帯の構成／★3町でサービスの整い方が異なること（自給率）／圏域内に事業所が存在しないサービスがあること</t>
+          <t>人口と高齢化の推移／要介護認定者数と認定率／高齢者のいる世帯の構成／3町でサービスの整い方が異なること（自給率）／圏域内に事業所が存在しないサービスがあること</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>要介護認定者数の見込み（令和9〜11年度）／主なサービスの見込量／給付費の見込み／★保険料基準額の試算と、そうなる理由／介護給付費準備基金の考え方／低所得者への軽減</t>
+          <t>要介護認定者数の見込み（令和9〜11年度）／主なサービスの見込量／給付費の見込み／保険料基準額の試算と、そうなる理由／介護給付費準備基金の考え方／低所得者への軽減</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>計画の進め方（毎年度の点検・公表＝PDCA）／★パブリックコメントの意見提出方法・期限・提出先／本編の入手方法（URL・閲覧場所）／問合せ先（大雪地区広域連合）／用語の説明（5〜8語）</t>
+          <t>計画の進め方（毎年度の点検・公表＝PDCA）／パブリックコメントの意見提出方法・期限・提出先／本編の入手方法（URL・閲覧場所）／問合せ先（大雪地区広域連合）／用語の説明（5〜8語）</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1931,7 +1931,7 @@
     <row r="14" ht="39" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>注1）★を付した要素は、本計画に固有の内容であり、一般的な概要版には現れない。3町の地域差（p3）と保険料の理由（p7）は、本計画の中心的な発見である。注2）p6は文字中心とし、図表を置かない。5基本目標×3〜4件＝15〜20件の取組を並べるため、図表を入れる余白がない。注3）論点は6件とした。パブリックコメントで住民が判断できる論点の数として6件を上限と考えている。論点を増やす場合は頁数の増加を伴う。注4）用語の説明（p8）に載せる語は05シートの【2】による。</t>
+          <t>注1）を付した要素は、本計画に固有の内容であり、一般的な概要版には現れない。3町の地域差（p3）と保険料の理由（p7）は、本計画の中心的な発見である。注2）p6は文字中心とし、図表を置かない。5基本目標×3〜4件＝15〜20件の取組を並べるため、図表を入れる余白がない。注3）論点は6件とした。パブリックコメントで住民が判断できる論点の数として6件を上限と考えている。論点を増やす場合は頁数の増加を伴う。注4）用語の説明（p8）に載せる語は05シートの【2】による。</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>★最も密度が高い頁になる</t>
+          <t>最も密度が高い頁になる</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>★本計画に固有の発見である。「使いたくても圏域内にない」ことは住民の実感と直結する</t>
+          <t>本計画に固有の発見である。「使いたくても圏域内にない」ことは住民の実感と直結する</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>★保険料が「なぜその額か」を示せる唯一の図である。第9期に基金の取崩しで基準額を抑えた経過が分かる</t>
+          <t>保険料が「なぜその額か」を示せる唯一の図である。第9期に基金の取崩しで基準額を抑えた経過が分かる</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -2880,7 +2880,7 @@
       <c r="D26" s="9" t="n"/>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>★1町のみの情報であり、概要版に載せると町の扱いが不均衡になる</t>
+          <t>1町のみの情報であり、概要版に載せると町の扱いが不均衡になる</t>
         </is>
       </c>
       <c r="F26" s="9" t="n"/>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>★保険料は例外とする。「試算値であり確定していない」ことを明示して載せる</t>
+          <t>保険料は例外とする。「試算値であり確定していない」ことを明示して載せる</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>★1町の情報が多いと、その町のための計画と受け取られる。</t>
+          <t>1町の情報が多いと、その町のための計画と受け取られる。</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="D17" s="17" t="inlineStr">
         <is>
-          <t>★用語の説明に載せる</t>
+          <t>用語の説明に載せる</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
-          <t>★用語の説明に載せる</t>
+          <t>用語の説明に載せる</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>
-          <t>★用語の説明に載せる</t>
+          <t>用語の説明に載せる</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="D23" s="18" t="inlineStr">
         <is>
-          <t>★用いない</t>
+          <t>用いない</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="D24" s="17" t="inlineStr">
         <is>
-          <t>★用語の説明に載せる</t>
+          <t>用語の説明に載せる</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>★パブリックコメント用の原稿を作成する</t>
+          <t>パブリックコメント用の原稿を作成する</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>★第1版を公表する</t>
+          <t>第1版を公表する</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>★第2版（最終版）を納品する</t>
+          <t>第2版（最終版）を納品する</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>★最大の差分である</t>
+          <t>最大の差分である</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>★意見の反映結果の概要に差し替える</t>
+          <t>意見の反映結果の概要に差し替える</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>★頁がずれるため、全箇所の付け替えを要する</t>
+          <t>頁がずれるため、全箇所の付け替えを要する</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>★具体の施策の要望が集まる。最も意見が出やすい論点である</t>
+          <t>具体の施策の要望が集まる。最も意見が出やすい論点である</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>★保険料の引下げ要望。基金をもっと取り崩すべきという意見</t>
+          <t>保険料の引下げ要望。基金をもっと取り崩すべきという意見</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>★試算値であることを明示して掲載する。確定値は第2版で差し替える。掲載しない案・公表を遅らせる案もある。</t>
+          <t>試算値であることを明示して掲載する。確定値は第2版で差し替える。掲載しない案・公表を遅らせる案もある。</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -4375,7 +4375,7 @@
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>★町別の比較は掲載し、事業所単位の情報は掲載しない。</t>
+          <t>町別の比較は掲載し、事業所単位の情報は掲載しない。</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>★パブリックコメント用（令和8年12月）と最終版（令和9年3月）の2版を作成する。</t>
+          <t>パブリックコメント用（令和8年12月）と最終版（令和9年3月）の2版を作成する。</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>★第1版と第2版で頁割を変えないことを前提にしている。第2版で論点欄を削るなら、その分の余白の使い方を先に決めておく必要がある。06シートの差分④に「意見の反映結果の概要」を充てる案を置いた</t>
+          <t>第1版と第2版で頁割を変えないことを前提にしている。第2版で論点欄を削るなら、その分の余白の使い方を先に決めておく必要がある。06シートの差分④に「意見の反映結果の概要」を充てる案を置いた</t>
         </is>
       </c>
     </row>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>第9期の概要版が存在し、その頁数が分かれば比較の基準になる（決定事項No.2）。★実施済み3調査に情報入手経路を尋ねた設問はないため、住民の情報接触の実態からは判断できない。第9期の概要版と、3町の広報紙の配布方法（全戸配布か、希望者配布か）が分かれば、分量の判断材料になる</t>
+          <t>第9期の概要版が存在し、その頁数が分かれば比較の基準になる（決定事項No.2）。実施済み3調査に情報入手経路を尋ねた設問はないため、住民の情報接触の実態からは判断できない。第9期の概要版と、3町の広報紙の配布方法（全戸配布か、希望者配布か）が分かれば、分量の判断材料になる</t>
         </is>
       </c>
     </row>
@@ -4754,7 +4754,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>★試算の前提（介護報酬改定率0％・基金取崩しなし等）を明記し、前提が変われば額が変わることを示す。あるいは幅（○円〜○円）で示す。受託者は幅で示す案を推奨する。決定事項No.3に反映する</t>
+          <t>試算の前提（介護報酬改定率0％・基金取崩しなし等）を明記し、前提が変われば額が変わることを示す。あるいは幅（○円〜○円）で示す。受託者は幅で示す案を推奨する。決定事項No.3に反映する</t>
         </is>
       </c>
     </row>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>図24-2を広域連合全体の図とし、町別に分解しない形で載せる。町別の不存在は本編に譲る。★04シートの選定を見直す余地がある</t>
+          <t>図24-2を広域連合全体の図とし、町別に分解しない形で載せる。町別の不存在は本編に譲る。04シートの選定を見直す余地がある</t>
         </is>
       </c>
     </row>
@@ -4808,7 +4808,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>★「以下の点に限らず、計画全体についてご意見をお寄せください」の一文を裏表紙に置く。論点は「考えていただきたい点」として示し、意見の範囲を限定しない表現とする</t>
+          <t>「以下の点に限らず、計画全体についてご意見をお寄せください」の一文を裏表紙に置く。論点は「考えていただきたい点」として示し、意見の範囲を限定しない表現とする</t>
         </is>
       </c>
     </row>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>図表集（白黒）が既にあるため、そちらの版を用いる。★概要版は本編と同じ白黒の図表を用い、多色化しない案に改める余地がある。決定事項No.2に含める</t>
+          <t>図表集（白黒）が既にあるため、そちらの版を用いる。概要版は本編と同じ白黒の図表を用い、多色化しない案に改める余地がある。決定事項No.2に含める</t>
         </is>
       </c>
     </row>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>施策体系図（p5）をp6に移し、p5とp6を見開きとして扱う。★03シートの頁割で、p5・p6を一体として設計する案がある</t>
+          <t>施策体系図（p5）をp6に移し、p5とp6を見開きとして扱う。03シートの頁割で、p5・p6を一体として設計する案がある</t>
         </is>
       </c>
     </row>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>頁割・体裁・図表の選定を令和8年10月までに済ませ、12月は数値の流し込みのみとする。★本表の決定事項の期限を令和8年10月としているのはこのためである</t>
+          <t>頁割・体裁・図表の選定を令和8年10月までに済ませ、12月は数値の流し込みのみとする。本表の決定事項の期限を令和8年10月としているのはこのためである</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_概要版の構成案.xlsx
+++ b/output/第10期計画_概要版の構成案.xlsx
@@ -1028,17 +1028,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>保険料が確定していない</t>
+          <t>保険料が確定していない（暫定の算定はある）</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>介護報酬改定率は令和8年12月頃、基金残高・収納率は令和8年度決算見込みによる。パブリックコメントの時点では確定していない。</t>
+          <t>介護報酬改定率は令和8年12月頃、令和7年度末の基金残高は令和8年12月頃による。パブリックコメントの時点では確定していない。受託者の暫定算定（将来推計 第3段階）では月額6,684円で、第9期の6,400円を284円上回る。基金を全額取り崩す場合は5,962円まで下がる。</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>試算値であることを明示して幅で示す（00シート④）。確定後に最終版で差し替える</t>
+          <t>試算値であることを明示して幅で示す（00シート④）。「どの前提でその水準になるか」を1文で添える。確定後に最終版で差し替える</t>
         </is>
       </c>
     </row>
@@ -1779,6 +1779,7 @@
         <is>
           <t>図19 第9期代表KPIの
 達成状況
+図31-1 第9期の対計画比
 図26-2 指標群別の得点</t>
         </is>
       </c>
@@ -1885,8 +1886,8 @@
       <c r="E12" s="5" t="inlineStr">
         <is>
           <t>図01 人口の推移と将来推計
-図29-1 必要保険料月額と
-条例上の基準額</t>
+図33-1 期別の保険料基準額
+（計画と実績）</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">

--- a/output/第10期計画_概要版の構成案.xlsx
+++ b/output/第10期計画_概要版の構成案.xlsx
@@ -1033,7 +1033,7 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>介護報酬改定率は令和8年12月頃、令和7年度末の基金残高は令和8年12月頃による。パブリックコメントの時点では確定していない。受託者の暫定算定（将来推計 第3段階）では月額6,684円で、第9期の6,400円を284円上回る。基金を全額取り崩す場合は5,962円まで下がる。</t>
+          <t>介護報酬改定率は令和8年12月頃、令和7年度末の基金残高は令和8年12月頃による。パブリックコメントの時点では確定していない。受託者の暫定算定（将来推計 第3段階）では月額6,755円で、第9期の6,400円を284円上回る。基金を全額取り崩す場合は5,962円まで下がる。</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">

--- a/output/第10期計画_概要版の構成案.xlsx
+++ b/output/第10期計画_概要版の構成案.xlsx
@@ -1033,7 +1033,7 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>介護報酬改定率は令和8年12月頃、令和7年度末の基金残高は令和8年12月頃による。パブリックコメントの時点では確定していない。受託者の暫定算定（将来推計 第3段階）では月額6,755円で、第9期の6,400円を284円上回る。基金を全額取り崩す場合は5,962円まで下がる。</t>
+          <t>介護報酬改定率は令和8年12月頃、令和7年度末の基金残高は令和8年12月頃による。パブリックコメントの時点では確定していない。受託者の暫定算定（将来推計 第3段階）では月額6,740円で、第9期の6,400円を284円上回る。基金を全額取り崩す場合は5,962円まで下がる。</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
